--- a/Informe de mensajeríaResumen38009620260505101900.xlsx
+++ b/Informe de mensajeríaResumen38009620260505101900.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srSkimberlyn\Desktop\Cientifico-de-datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82315BF6-0C7A-4A38-A18E-22BB6C5509B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E32327-D0F7-4A6E-8A55-B1AC59970FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet0" sheetId="1" r:id="rId1"/>
@@ -2093,9 +2093,11 @@
   <dimension ref="A1:AA622"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
     <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.81640625" customWidth="1"/>
     <col min="24" max="24" width="23.08984375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18.08984375" bestFit="1" customWidth="1"/>
